--- a/internal_doc/05.测试设计/story/alter/altercs测试用例（cs基本功能）.xlsx
+++ b/internal_doc/05.测试设计/story/alter/altercs测试用例（cs基本功能）.xlsx
@@ -85,10 +85,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、修改成功，快照（snapshot（5））查看cs属性信息中pageSize属性值和修改值一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cs中存在cl，修改pageSize属性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,10 +112,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、修改成功，快照（snapshot（5））查看cs属性信息中LobpageSize属性值和修改值一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cs中存在cl，修改LobpageSize属性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -132,11 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a场景：修改失败，返回对应错误信息，查看cs属性信息中LobPageSize值未更新
-b场景：修改成功，快照（snapshot（5））查看cs属性信息中LobPageSize属性值和修改值一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>新增domain，domain包含cs所在组</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -290,6 +277,19 @@
   </si>
   <si>
     <t>2、检查操作结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改成功，快照（snapshot（5））查看cs属性信息中pageSize属性值和修改值一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a场景：修改失败，返回对应错误信息，查看cs属性信息中LobPageSize值未更新
+b场景：修改成功，快照（snapshot（5））查看cs属性信息中LobPageSize属性值和修改值一致，查看数据节点上对应属性值已更新（直连数据节点查看cl属性中lobpagesize值）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改成功，快照（snapshot（5））查看cs属性信息中LobpageSize属性值和修改值一致，查看数据节点上对应属性值已更新（直连数据节点查看cl属性中lobpagesize值）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -912,7 +912,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I3" s="3">
         <v>1</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I4" s="3">
         <v>1</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="5" spans="1:9" ht="54">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="I5" s="3">
         <v>1</v>
@@ -972,7 +972,7 @@
     </row>
     <row r="6" spans="1:9" ht="81">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
@@ -987,10 +987,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -998,82 +998,82 @@
     </row>
     <row r="7" spans="1:9" ht="81">
       <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="94.5">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="81">
       <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="94.5">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1085,19 +1085,19 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="94.5">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -1109,67 +1109,67 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" ht="108">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:9" ht="81">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="40.5">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1181,10 +1181,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
